--- a/data/metadata_raw/wholesale_trade.xlsx
+++ b/data/metadata_raw/wholesale_trade.xlsx
@@ -521,7 +521,7 @@
     <t>2022-08-22</t>
   </si>
   <si>
-    <t>2024-08-23</t>
+    <t>2025-07-04</t>
   </si>
   <si>
     <t>1.07.01.0001</t>
